--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486510_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486510_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7168</v>
+        <v>2.7042</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0541</v>
+        <v>1.8875</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6627</v>
+        <v>0.8168</v>
       </c>
       <c r="G2" t="n">
         <v>-0.6473</v>
@@ -610,13 +610,13 @@
         <v>3.2626</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1721</v>
+        <v>0.1595</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4395</v>
+        <v>0.2728</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2674</v>
+        <v>-0.1133</v>
       </c>
       <c r="V2" t="n">
         <v>1.017</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3185</v>
+        <v>1.4362</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0422</v>
+        <v>2.0674</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7237</v>
+        <v>-0.6312</v>
       </c>
       <c r="G3" t="n">
         <v>-1.1729</v>
@@ -688,13 +688,13 @@
         <v>0.6525</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0513</v>
+        <v>0.0664</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0721</v>
+        <v>0.0973</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1234</v>
+        <v>-0.031</v>
       </c>
       <c r="V3" t="n">
         <v>1.8902</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1267</v>
+        <v>0.0343</v>
       </c>
       <c r="E4" t="n">
         <v>0.6784</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5516</v>
+        <v>-0.6441</v>
       </c>
       <c r="G4" t="n">
         <v>1.7395</v>
@@ -766,13 +766,13 @@
         <v>1.9576</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0429</v>
+        <v>-0.0496</v>
       </c>
       <c r="T4" t="n">
         <v>-0.2019</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2448</v>
+        <v>0.1523</v>
       </c>
       <c r="V4" t="n">
         <v>-1.4382</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1058</v>
+        <v>-0.6327</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4331</v>
+        <v>0.1942</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6727</v>
+        <v>-0.8268</v>
       </c>
       <c r="G5" t="n">
         <v>-2.7514</v>
@@ -844,13 +844,13 @@
         <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0292</v>
+        <v>-0.5561</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4264</v>
+        <v>-0.7991</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3972</v>
+        <v>0.243</v>
       </c>
       <c r="V5" t="n">
         <v>0.9347</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2395</v>
+        <v>-0.8657</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4195</v>
+        <v>-0.8607</v>
       </c>
       <c r="F6" t="n">
-        <v>0.18</v>
+        <v>-0.0049</v>
       </c>
       <c r="G6" t="n">
         <v>-2.7641</v>
@@ -922,13 +922,13 @@
         <v>2.8276</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8203</v>
+        <v>-0.4464</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7498</v>
+        <v>-0.1911</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0704</v>
+        <v>-0.2554</v>
       </c>
       <c r="V6" t="n">
         <v>-0.4828</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>M. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0873</v>
+        <v>-2.3431</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4238</v>
+        <v>0.4137</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6636</v>
+        <v>-2.7568</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7517</v>
+        <v>-4.1951</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.323</v>
+        <v>-5.6446</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4287</v>
+        <v>1.4495</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6703</v>
+        <v>-1.5645</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7086</v>
+        <v>-3.2873</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0382</v>
+        <v>1.7228</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0814</v>
+        <v>-2.6307</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-2.3573</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.467</v>
+        <v>-0.2733</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6525</v>
+        <v>2.6101</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.435</v>
+        <v>2.6101</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3169</v>
+        <v>-0.8403</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3341</v>
+        <v>-0.4771</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0172</v>
+        <v>-0.3632</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.0822</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.4552</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.3729</v>
       </c>
     </row>
     <row r="8">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6035</v>
+        <v>-2.38</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1186</v>
+        <v>-2.8951</v>
       </c>
       <c r="F8" t="n">
         <v>0.5151</v>
@@ -1078,10 +1078,10 @@
         <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2055</v>
+        <v>0.018</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4675</v>
+        <v>-0.2439</v>
       </c>
       <c r="U8" t="n">
         <v>0.262</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. JORDA RODRIGUEZ</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4579</v>
+        <v>-2.5584</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7995</v>
+        <v>-1.8023</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6584</v>
+        <v>-0.7561</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8879</v>
+        <v>-1.7517</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3436</v>
+        <v>-1.323</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5443</v>
+        <v>-0.4287</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5666</v>
+        <v>-0.6703</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5538</v>
+        <v>-0.7086</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.1204</v>
+        <v>0.0382</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3213</v>
+        <v>-1.0814</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8974</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5760999999999999</v>
+        <v>-0.467</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5225</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9626</v>
+        <v>-0.1541</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2329</v>
+        <v>-0.0445</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7297</v>
+        <v>-0.1097</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. TORRES CUEVAS</t>
+          <t>A. JORDA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6263</v>
+        <v>-2.8508</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-2.439</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0342</v>
+        <v>-0.4118</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.1951</v>
+        <v>-1.8879</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.6446</v>
+        <v>-0.3436</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4495</v>
+        <v>-1.5443</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5645</v>
+        <v>-1.5666</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.2873</v>
+        <v>0.5538</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7228</v>
+        <v>-2.1204</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.6307</v>
+        <v>-0.3213</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.3573</v>
+        <v>-0.8974</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2733</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6101</v>
+        <v>1.5225</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6101</v>
+        <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1235</v>
+        <v>-1.3555</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.4829</v>
+        <v>-0.8724</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6405999999999999</v>
+        <v>-0.4831</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0822</v>
+        <v>-1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4552</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3729</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6735</v>
+        <v>-3.605</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6682</v>
+        <v>-2.5997</v>
       </c>
       <c r="F11" t="n">
         <v>-1.0053</v>
@@ -1312,10 +1312,10 @@
         <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.536</v>
+        <v>-0.4675</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2019</v>
+        <v>-0.1334</v>
       </c>
       <c r="U11" t="n">
         <v>-0.3341</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4299</v>
+        <v>-5.316</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.8161</v>
+        <v>-5.4556</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3862</v>
+        <v>0.1397</v>
       </c>
       <c r="G12" t="n">
         <v>-4.452</v>
@@ -1390,13 +1390,13 @@
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7604</v>
+        <v>-0.6465</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0959</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3355</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.0617</v>
+        <v>-16.377</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.4963</v>
+        <v>-10.8112</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.5655</v>
+        <v>-5.5654</v>
       </c>
       <c r="G13" t="n">
         <v>-22.436</v>
@@ -1447,7 +1447,7 @@
         <v>-6.429600000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4982000000000002</v>
+        <v>0.4981999999999993</v>
       </c>
       <c r="M13" t="n">
         <v>-16.505</v>
@@ -1456,7 +1456,7 @@
         <v>-16.1062</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3987000000000002</v>
+        <v>-0.3986999999999999</v>
       </c>
       <c r="P13" t="n">
         <v>10.8754</v>
@@ -1468,28 +1468,28 @@
         <v>18.488</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.9569</v>
+        <v>-4.2721</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.013500000000001</v>
+        <v>-3.3287</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9432999999999999</v>
+        <v>-0.9436</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5444</v>
+        <v>-0.5443999999999998</v>
       </c>
       <c r="W13" t="n">
         <v>6.061</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.6053</v>
+        <v>-6.605300000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. NGOM</t>
+          <t>J. TATE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.565200000000001</v>
+        <v>6.8056</v>
       </c>
       <c r="E14" t="n">
-        <v>5.754</v>
+        <v>6.6187</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8112</v>
+        <v>0.1869</v>
       </c>
       <c r="G14" t="n">
-        <v>5.8385</v>
+        <v>6.2478</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3643</v>
+        <v>5.5689</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4742</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>5.3701</v>
+        <v>6.6138</v>
       </c>
       <c r="K14" t="n">
-        <v>4.0696</v>
+        <v>4.6631</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3005</v>
+        <v>1.9507</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4684</v>
+        <v>-0.366</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2947</v>
+        <v>0.9058</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1737</v>
+        <v>-1.2718</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>-2.3926</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S14" t="n">
-        <v>3.8567</v>
+        <v>0.2331</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2762</v>
+        <v>-0.0577</v>
       </c>
       <c r="U14" t="n">
-        <v>2.5805</v>
+        <v>0.2908</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.13</v>
+        <v>2.0647</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1952</v>
+        <v>2.4552</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.3252</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. TATE</t>
+          <t>A. NGOM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.4677</v>
+        <v>6.758</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0599</v>
+        <v>4.7482</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4077</v>
+        <v>2.0098</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2478</v>
+        <v>5.8385</v>
       </c>
       <c r="H15" t="n">
-        <v>5.5689</v>
+        <v>4.3643</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6788999999999999</v>
+        <v>1.4742</v>
       </c>
       <c r="J15" t="n">
-        <v>6.6138</v>
+        <v>5.3701</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6631</v>
+        <v>4.0696</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9507</v>
+        <v>1.3005</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.366</v>
+        <v>0.4684</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9058</v>
+        <v>0.2947</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2718</v>
+        <v>0.1737</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.7401</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3926</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1048</v>
+        <v>2.0495</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6165</v>
+        <v>0.2704</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5117</v>
+        <v>1.7791</v>
       </c>
       <c r="V15" t="n">
-        <v>2.0647</v>
+        <v>-1.13</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4552</v>
+        <v>0.1952</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3904</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8989</v>
+        <v>5.2026</v>
       </c>
       <c r="E16" t="n">
-        <v>5.5904</v>
+        <v>4.4728</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3085</v>
+        <v>0.7298</v>
       </c>
       <c r="G16" t="n">
         <v>4.1224</v>
@@ -1702,13 +1702,13 @@
         <v>0.6525</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2142</v>
+        <v>0.5179</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8242</v>
+        <v>0.7066</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.61</v>
+        <v>-0.1887</v>
       </c>
       <c r="V16" t="n">
         <v>3.3899</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2144</v>
+        <v>3.1187</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7438</v>
+        <v>-0.2968</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9582</v>
+        <v>3.4154</v>
       </c>
       <c r="G17" t="n">
         <v>2.5809</v>
@@ -1780,13 +1780,13 @@
         <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.149</v>
+        <v>0.7553</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.536</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3869</v>
+        <v>0.8442</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>T. MCGHIE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6302</v>
+        <v>2.4281</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7542</v>
+        <v>1.7777</v>
       </c>
       <c r="F18" t="n">
-        <v>3.3845</v>
+        <v>0.6504</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2019</v>
+        <v>2.4276</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7876</v>
+        <v>2.4723</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5857</v>
+        <v>-0.0446</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7184</v>
+        <v>2.3952</v>
       </c>
       <c r="K18" t="n">
-        <v>0.657</v>
+        <v>1.168</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3754</v>
+        <v>1.2272</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9203</v>
+        <v>0.0325</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1306</v>
+        <v>1.3043</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7897</v>
+        <v>-1.2718</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.0875</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3926</v>
+        <v>-1.305</v>
       </c>
       <c r="R18" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1461</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3567</v>
+        <v>0.1226</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7894</v>
+        <v>-0.0346</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3698</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. MCGHIE</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3928</v>
+        <v>0.7901</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1071</v>
+        <v>-2.8718</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2857</v>
+        <v>3.6619</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4276</v>
+        <v>0.2019</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4723</v>
+        <v>0.7876</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0446</v>
+        <v>-0.5857</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3952</v>
+        <v>-0.7184</v>
       </c>
       <c r="K19" t="n">
-        <v>1.168</v>
+        <v>0.657</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2272</v>
+        <v>-1.3754</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0325</v>
+        <v>0.9203</v>
       </c>
       <c r="N19" t="n">
-        <v>1.3043</v>
+        <v>0.1306</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2718</v>
+        <v>0.7897</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6525</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.305</v>
+        <v>-2.3926</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9473</v>
+        <v>1.3059</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.548</v>
+        <v>0.2392</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3993</v>
+        <v>1.0668</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.3698</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0053</v>
+        <v>0.0361</v>
       </c>
       <c r="E20" t="n">
         <v>0.0182</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0129</v>
+        <v>0.0179</v>
       </c>
       <c r="G20" t="n">
         <v>0.1338</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0753</v>
+        <v>-0.0478</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0153</v>
+        <v>-3.5683</v>
       </c>
       <c r="F22" t="n">
-        <v>2.9399</v>
+        <v>3.5205</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7225</v>
@@ -2170,13 +2170,13 @@
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1353</v>
+        <v>0.8923</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6044</v>
+        <v>-0.1574</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4691</v>
+        <v>1.0497</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1571</v>
+        <v>-0.4879</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3118</v>
+        <v>-3.9766</v>
       </c>
       <c r="F23" t="n">
-        <v>3.1548</v>
+        <v>3.4887</v>
       </c>
       <c r="G23" t="n">
         <v>-0.1961</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0257</v>
+        <v>0.6435</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6044</v>
+        <v>-0.2692</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5787</v>
+        <v>0.9127</v>
       </c>
       <c r="V23" t="n">
         <v>0.3698</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3702</v>
+        <v>-2.1556</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.06370000000000001</v>
+        <v>0.4951</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3065</v>
+        <v>-2.6507</v>
       </c>
       <c r="G24" t="n">
         <v>1.2257</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1185</v>
+        <v>0.0961</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.548</v>
+        <v>0.0108</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4295</v>
+        <v>0.0853</v>
       </c>
       <c r="V24" t="n">
         <v>-2.8249</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.4948</v>
+        <v>-3.8808</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.0936</v>
+        <v>-1.8701</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.4011</v>
+        <v>-2.0106</v>
       </c>
       <c r="G25" t="n">
         <v>0.5911999999999999</v>
@@ -2404,13 +2404,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.651</v>
+        <v>-0.037</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0565</v>
+        <v>0.167</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5945</v>
+        <v>-0.204</v>
       </c>
       <c r="V25" t="n">
         <v>-2.2599</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>17.0619</v>
+        <v>18.5519</v>
       </c>
       <c r="E26" t="n">
-        <v>5.565399999999999</v>
+        <v>5.565299999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>11.4965</v>
+        <v>12.9865</v>
       </c>
       <c r="G26" t="n">
         <v>22.436</v>
@@ -2482,13 +2482,13 @@
         <v>7.6125</v>
       </c>
       <c r="S26" t="n">
-        <v>4.9569</v>
+        <v>6.447</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9432999999999996</v>
+        <v>0.9434000000000002</v>
       </c>
       <c r="U26" t="n">
-        <v>4.0135</v>
+        <v>5.5037</v>
       </c>
       <c r="V26" t="n">
         <v>0.5444</v>
